--- a/models/plantilla_informe_he.xlsx
+++ b/models/plantilla_informe_he.xlsx
@@ -541,40 +541,44 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="46">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -582,19 +586,19 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="true"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -602,123 +606,123 @@
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="true"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="21" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="21" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="21" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="21" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -813,9 +817,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>109440</xdr:colOff>
+      <xdr:colOff>109080</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>1054440</xdr:rowOff>
+      <xdr:rowOff>1054080</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -829,7 +833,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="2038680" cy="1054440"/>
+          <a:ext cx="2038320" cy="1054080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -851,9 +855,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>7870320</xdr:colOff>
+      <xdr:colOff>7869960</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>399960</xdr:rowOff>
+      <xdr:rowOff>399600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -866,8 +870,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10009800" y="21960"/>
-          <a:ext cx="4150080" cy="378000"/>
+          <a:off x="10010520" y="21960"/>
+          <a:ext cx="4149720" cy="377640"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -997,930 +1001,926 @@
   <dimension ref="A1:N37"/>
   <sheetFormatPr defaultColWidth="8.8984375" defaultRowHeight="15.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11.8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="3" style="0" width="6.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="9.9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="101.6"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="11" min="11" style="0" width="7.9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="8.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="12.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="3.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="3" style="1" width="6.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="2" width="9.9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="101.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="7.9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="8.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="12.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="3.3"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="84.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="6" t="s">
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="7" t="n">
+      <c r="I2" s="8" t="n">
         <f aca="false">SUM(K6:K36)</f>
         <v>52.5166666666667</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="J2" s="9" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="9"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="6" t="s">
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="11" t="n">
+      <c r="I3" s="12" t="n">
         <f aca="false">SUM(I6:I36)</f>
         <v>1.31875</v>
       </c>
-      <c r="J3" s="12" t="s">
+      <c r="J3" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="K3" s="13"/>
-      <c r="L3" s="13"/>
-      <c r="M3" s="13"/>
-      <c r="N3" s="13"/>
-    </row>
-    <row r="4" s="20" customFormat="true" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="14" t="s">
+      <c r="K3" s="14"/>
+      <c r="L3" s="14"/>
+      <c r="M3" s="14"/>
+      <c r="N3" s="14"/>
+    </row>
+    <row r="4" s="21" customFormat="true" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="14"/>
-      <c r="C4" s="14"/>
-      <c r="D4" s="14"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="15"/>
-      <c r="H4" s="16" t="str">
+      <c r="B4" s="15"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="17" t="str">
         <f aca="false">UPPER(TEXT(B6, "mmmm aaaa"))</f>
         <v>MAYO 2026</v>
       </c>
-      <c r="I4" s="17"/>
-      <c r="J4" s="18" t="s">
+      <c r="I4" s="18"/>
+      <c r="J4" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="K4" s="19"/>
-      <c r="L4" s="19"/>
-      <c r="M4" s="19"/>
-      <c r="N4" s="19"/>
-    </row>
-    <row r="5" s="26" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="21" t="s">
+      <c r="K4" s="20"/>
+      <c r="L4" s="20"/>
+      <c r="M4" s="20"/>
+      <c r="N4" s="20"/>
+    </row>
+    <row r="5" s="27" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="23" t="s">
+      <c r="C5" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="23" t="s">
+      <c r="D5" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="23" t="s">
+      <c r="E5" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="22" t="s">
+      <c r="F5" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="G5" s="23" t="s">
+      <c r="G5" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="H5" s="23" t="s">
+      <c r="H5" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="I5" s="23" t="s">
+      <c r="I5" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="J5" s="24" t="s">
+      <c r="J5" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="K5" s="25"/>
-      <c r="L5" s="25"/>
-      <c r="M5" s="25"/>
-      <c r="N5" s="25"/>
+      <c r="K5" s="26"/>
+      <c r="L5" s="26"/>
+      <c r="M5" s="26"/>
+      <c r="N5" s="26"/>
     </row>
     <row r="6" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="27" t="str">
+      <c r="A6" s="28" t="str">
         <f aca="false">IF(B6&gt;0,PROPER(TEXT(B6,"dddd")),"")</f>
         <v>Viernes</v>
       </c>
-      <c r="B6" s="28" t="n">
+      <c r="B6" s="29" t="n">
         <v>46143</v>
       </c>
-      <c r="C6" s="29"/>
-      <c r="D6" s="30"/>
-      <c r="E6" s="29"/>
-      <c r="F6" s="30"/>
-      <c r="G6" s="29"/>
-      <c r="H6" s="30"/>
-      <c r="I6" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="31" t="s">
+      <c r="C6" s="30"/>
+      <c r="D6" s="31"/>
+      <c r="E6" s="30"/>
+      <c r="F6" s="31"/>
+      <c r="G6" s="30"/>
+      <c r="H6" s="31"/>
+      <c r="I6" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="K6" s="0" t="n">
+      <c r="K6" s="1" t="n">
         <f aca="true" t="array" ref="K6:K6">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*2*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*2*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*2*24)</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="27" t="str">
+      <c r="A7" s="28" t="str">
         <f aca="false">IF(B7&gt;0,PROPER(TEXT(B7,"dddd")),"")</f>
         <v>Sábado</v>
       </c>
-      <c r="B7" s="32" t="n">
+      <c r="B7" s="33" t="n">
         <v>46144</v>
       </c>
-      <c r="C7" s="33" t="n">
+      <c r="C7" s="34" t="n">
         <v>0.803472222222222</v>
       </c>
-      <c r="D7" s="34" t="n">
+      <c r="D7" s="35" t="n">
         <v>0.865277777777778</v>
       </c>
-      <c r="E7" s="33"/>
-      <c r="F7" s="34"/>
-      <c r="G7" s="33"/>
-      <c r="H7" s="34"/>
-      <c r="I7" s="33" t="n">
+      <c r="E7" s="34"/>
+      <c r="F7" s="35"/>
+      <c r="G7" s="34"/>
+      <c r="H7" s="35"/>
+      <c r="I7" s="34" t="n">
         <v>0.0618055555555556</v>
       </c>
-      <c r="J7" s="31" t="s">
+      <c r="J7" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="K7" s="0" t="n">
+      <c r="K7" s="1" t="n">
         <f aca="true" t="array" ref="K7:K7">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*2*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*2*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*2*24)</f>
         <v>2.96666666666667</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="27" t="str">
+      <c r="A8" s="28" t="str">
         <f aca="false">IF(B8&gt;0,PROPER(TEXT(B8,"dddd")),"")</f>
         <v>Domingo</v>
       </c>
-      <c r="B8" s="32" t="n">
+      <c r="B8" s="33" t="n">
         <v>46145</v>
       </c>
-      <c r="C8" s="33" t="n">
+      <c r="C8" s="34" t="n">
         <v>0.370138888888889</v>
       </c>
-      <c r="D8" s="34" t="n">
+      <c r="D8" s="35" t="n">
         <v>0.552083333333333</v>
       </c>
-      <c r="E8" s="33" t="n">
+      <c r="E8" s="34" t="n">
         <v>0.709027777777778</v>
       </c>
-      <c r="F8" s="34" t="n">
+      <c r="F8" s="35" t="n">
         <v>0.795138888888889</v>
       </c>
-      <c r="G8" s="33"/>
-      <c r="H8" s="34"/>
-      <c r="I8" s="33" t="n">
+      <c r="G8" s="34"/>
+      <c r="H8" s="35"/>
+      <c r="I8" s="34" t="n">
         <v>0.268055555555556</v>
       </c>
-      <c r="J8" s="31" t="s">
+      <c r="J8" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="K8" s="0" t="n">
+      <c r="K8" s="1" t="n">
         <f aca="true" t="array" ref="K8:K8">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*2*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*2*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*2*24)</f>
         <v>12.8666666666667</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="27" t="str">
+      <c r="A9" s="28" t="str">
         <f aca="false">IF(B9&gt;0,PROPER(TEXT(B9,"dddd")),"")</f>
         <v>Lunes</v>
       </c>
-      <c r="B9" s="28" t="n">
+      <c r="B9" s="29" t="n">
         <v>46146</v>
       </c>
-      <c r="C9" s="33" t="n">
+      <c r="C9" s="34" t="n">
         <v>0.677777777777778</v>
       </c>
-      <c r="D9" s="34" t="n">
+      <c r="D9" s="35" t="n">
         <v>0.766666666666667</v>
       </c>
-      <c r="E9" s="33"/>
-      <c r="F9" s="34"/>
-      <c r="G9" s="33"/>
-      <c r="H9" s="34"/>
-      <c r="I9" s="33" t="n">
+      <c r="E9" s="34"/>
+      <c r="F9" s="35"/>
+      <c r="G9" s="34"/>
+      <c r="H9" s="35"/>
+      <c r="I9" s="34" t="n">
         <v>0.0888888888888889</v>
       </c>
-      <c r="J9" s="31" t="s">
+      <c r="J9" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="K9" s="0" t="n">
+      <c r="K9" s="1" t="n">
         <f aca="true" t="array" ref="K9:K9">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*1.5*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*1.5*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*1.5*24)</f>
         <v>3.2</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="27" t="str">
+      <c r="A10" s="28" t="str">
         <f aca="false">IF(B10&gt;0,PROPER(TEXT(B10,"dddd")),"")</f>
         <v>Martes</v>
       </c>
-      <c r="B10" s="32" t="n">
+      <c r="B10" s="33" t="n">
         <v>46147</v>
       </c>
-      <c r="C10" s="33" t="n">
+      <c r="C10" s="34" t="n">
         <v>0.366666666666667</v>
       </c>
-      <c r="D10" s="34" t="n">
+      <c r="D10" s="35" t="n">
         <v>0.450694444444444</v>
       </c>
-      <c r="E10" s="33"/>
-      <c r="F10" s="34"/>
-      <c r="G10" s="33"/>
-      <c r="H10" s="34"/>
-      <c r="I10" s="33" t="n">
+      <c r="E10" s="34"/>
+      <c r="F10" s="35"/>
+      <c r="G10" s="34"/>
+      <c r="H10" s="35"/>
+      <c r="I10" s="34" t="n">
         <v>0.0840277777777778</v>
       </c>
-      <c r="J10" s="31" t="s">
+      <c r="J10" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="K10" s="0" t="n">
+      <c r="K10" s="1" t="n">
         <f aca="true" t="array" ref="K10:K10">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*1.5*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*1.5*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*1.5*24)</f>
         <v>3.025</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="27" t="str">
+      <c r="A11" s="28" t="str">
         <f aca="false">IF(B11&gt;0,PROPER(TEXT(B11,"dddd")),"")</f>
         <v>Miércoles</v>
       </c>
-      <c r="B11" s="32" t="n">
+      <c r="B11" s="33" t="n">
         <v>46148</v>
       </c>
-      <c r="C11" s="33" t="n">
+      <c r="C11" s="34" t="n">
         <v>0.798611111111111</v>
       </c>
-      <c r="D11" s="34" t="n">
+      <c r="D11" s="35" t="n">
         <v>0.885416666666667</v>
       </c>
-      <c r="E11" s="33"/>
-      <c r="F11" s="34"/>
-      <c r="G11" s="33"/>
-      <c r="H11" s="34"/>
-      <c r="I11" s="35" t="n">
+      <c r="E11" s="34"/>
+      <c r="F11" s="35"/>
+      <c r="G11" s="34"/>
+      <c r="H11" s="35"/>
+      <c r="I11" s="36" t="n">
         <v>0.0868055555555556</v>
       </c>
-      <c r="J11" s="31" t="s">
+      <c r="J11" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="K11" s="0" t="n">
+      <c r="K11" s="1" t="n">
         <f aca="true" t="array" ref="K11:K11">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*1.5*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*1.5*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*1.5*24)</f>
         <v>3.125</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="27" t="str">
+      <c r="A12" s="28" t="str">
         <f aca="false">IF(B12&gt;0,PROPER(TEXT(B12,"dddd")),"")</f>
         <v>Jueves</v>
       </c>
-      <c r="B12" s="28" t="n">
+      <c r="B12" s="29" t="n">
         <v>46149</v>
       </c>
-      <c r="C12" s="33" t="n">
+      <c r="C12" s="34" t="n">
         <v>0.75</v>
       </c>
-      <c r="D12" s="34" t="n">
+      <c r="D12" s="35" t="n">
         <v>0.847222222222222</v>
       </c>
-      <c r="E12" s="33"/>
-      <c r="F12" s="34"/>
-      <c r="G12" s="33"/>
-      <c r="H12" s="34"/>
-      <c r="I12" s="36" t="n">
+      <c r="E12" s="34"/>
+      <c r="F12" s="35"/>
+      <c r="G12" s="34"/>
+      <c r="H12" s="35"/>
+      <c r="I12" s="37" t="n">
         <v>0.0972222222222222</v>
       </c>
-      <c r="J12" s="31" t="s">
+      <c r="J12" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="K12" s="0" t="n">
+      <c r="K12" s="1" t="n">
         <f aca="true" t="array" ref="K12:K12">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*1.5*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*1.5*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*1.5*24)</f>
         <v>3.5</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="27" t="str">
+      <c r="A13" s="28" t="str">
         <f aca="false">IF(B13&gt;0,PROPER(TEXT(B13,"dddd")),"")</f>
         <v>Viernes</v>
       </c>
-      <c r="B13" s="32" t="n">
+      <c r="B13" s="33" t="n">
         <v>46150</v>
       </c>
-      <c r="C13" s="33"/>
-      <c r="D13" s="34"/>
-      <c r="E13" s="33"/>
-      <c r="F13" s="34"/>
-      <c r="G13" s="33"/>
-      <c r="H13" s="34"/>
-      <c r="I13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="31"/>
-      <c r="K13" s="0" t="n">
+      <c r="C13" s="34"/>
+      <c r="D13" s="35"/>
+      <c r="E13" s="34"/>
+      <c r="F13" s="35"/>
+      <c r="G13" s="34"/>
+      <c r="H13" s="35"/>
+      <c r="I13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="32"/>
+      <c r="K13" s="1" t="n">
         <f aca="true" t="array" ref="K13:K13">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*1.5*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*1.5*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*1.5*24)</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="27" t="str">
+      <c r="A14" s="28" t="str">
         <f aca="false">IF(B14&gt;0,PROPER(TEXT(B14,"dddd")),"")</f>
         <v>Sábado</v>
       </c>
-      <c r="B14" s="32" t="n">
+      <c r="B14" s="33" t="n">
         <v>46151</v>
       </c>
-      <c r="C14" s="33"/>
-      <c r="D14" s="34"/>
-      <c r="E14" s="33"/>
-      <c r="F14" s="34"/>
-      <c r="G14" s="33"/>
-      <c r="H14" s="34"/>
-      <c r="I14" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="31"/>
-      <c r="K14" s="0" t="n">
+      <c r="C14" s="34"/>
+      <c r="D14" s="35"/>
+      <c r="E14" s="34"/>
+      <c r="F14" s="35"/>
+      <c r="G14" s="34"/>
+      <c r="H14" s="35"/>
+      <c r="I14" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="32"/>
+      <c r="K14" s="1" t="n">
         <f aca="true" t="array" ref="K14:K14">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*2*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*2*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*2*24)</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="27" t="str">
+      <c r="A15" s="28" t="str">
         <f aca="false">IF(B15&gt;0,PROPER(TEXT(B15,"dddd")),"")</f>
         <v>Domingo</v>
       </c>
-      <c r="B15" s="28" t="n">
+      <c r="B15" s="29" t="n">
         <v>46152</v>
       </c>
-      <c r="C15" s="33" t="n">
+      <c r="C15" s="34" t="n">
         <v>0.727083333333333</v>
       </c>
-      <c r="D15" s="34" t="n">
+      <c r="D15" s="35" t="n">
         <v>0.817361111111111</v>
       </c>
-      <c r="E15" s="33"/>
-      <c r="F15" s="34"/>
-      <c r="G15" s="33"/>
-      <c r="H15" s="34"/>
-      <c r="I15" s="33" t="n">
+      <c r="E15" s="34"/>
+      <c r="F15" s="35"/>
+      <c r="G15" s="34"/>
+      <c r="H15" s="35"/>
+      <c r="I15" s="34" t="n">
         <v>0.0902777777777778</v>
       </c>
-      <c r="J15" s="31" t="s">
+      <c r="J15" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="K15" s="0" t="n">
+      <c r="K15" s="1" t="n">
         <f aca="true" t="array" ref="K15:K15">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*2*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*2*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*2*24)</f>
         <v>4.33333333333333</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="27" t="str">
+      <c r="A16" s="28" t="str">
         <f aca="false">IF(B16&gt;0,PROPER(TEXT(B16,"dddd")),"")</f>
         <v>Lunes</v>
       </c>
-      <c r="B16" s="32" t="n">
+      <c r="B16" s="33" t="n">
         <v>46153</v>
       </c>
-      <c r="C16" s="33"/>
-      <c r="D16" s="34"/>
-      <c r="E16" s="33"/>
-      <c r="F16" s="34"/>
-      <c r="G16" s="33"/>
-      <c r="H16" s="34"/>
-      <c r="I16" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="31"/>
-      <c r="K16" s="0" t="n">
+      <c r="C16" s="34"/>
+      <c r="D16" s="35"/>
+      <c r="E16" s="34"/>
+      <c r="F16" s="35"/>
+      <c r="G16" s="34"/>
+      <c r="H16" s="35"/>
+      <c r="I16" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="32"/>
+      <c r="K16" s="1" t="n">
         <f aca="true" t="array" ref="K16:K16">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*1.5*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*1.5*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*1.5*24)</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="27" t="str">
+      <c r="A17" s="28" t="str">
         <f aca="false">IF(B17&gt;0,PROPER(TEXT(B17,"dddd")),"")</f>
         <v>Martes</v>
       </c>
-      <c r="B17" s="32" t="n">
+      <c r="B17" s="33" t="n">
         <v>46154</v>
       </c>
-      <c r="C17" s="33" t="n">
+      <c r="C17" s="34" t="n">
         <v>0.375</v>
       </c>
-      <c r="D17" s="34" t="n">
+      <c r="D17" s="35" t="n">
         <v>0.916666666666667</v>
       </c>
-      <c r="E17" s="33"/>
-      <c r="F17" s="34"/>
-      <c r="G17" s="33"/>
-      <c r="H17" s="34"/>
-      <c r="I17" s="33" t="n">
+      <c r="E17" s="34"/>
+      <c r="F17" s="35"/>
+      <c r="G17" s="34"/>
+      <c r="H17" s="35"/>
+      <c r="I17" s="34" t="n">
         <f aca="false">D17-C17</f>
         <v>0.541666666666667</v>
       </c>
-      <c r="J17" s="31"/>
-      <c r="K17" s="0" t="n">
+      <c r="J17" s="32"/>
+      <c r="K17" s="1" t="n">
         <f aca="true" t="array" ref="K17:K17">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*1.5*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*1.5*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*1.5*24)</f>
         <v>19.5</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="27" t="str">
+      <c r="A18" s="28" t="str">
         <f aca="false">IF(B18&gt;0,PROPER(TEXT(B18,"dddd")),"")</f>
         <v>Miércoles</v>
       </c>
-      <c r="B18" s="28" t="n">
+      <c r="B18" s="29" t="n">
         <v>46155</v>
       </c>
-      <c r="C18" s="33"/>
-      <c r="D18" s="34"/>
-      <c r="E18" s="33"/>
-      <c r="F18" s="34"/>
-      <c r="G18" s="33"/>
-      <c r="H18" s="34"/>
-      <c r="I18" s="33" t="n">
+      <c r="C18" s="34"/>
+      <c r="D18" s="35"/>
+      <c r="E18" s="34"/>
+      <c r="F18" s="35"/>
+      <c r="G18" s="34"/>
+      <c r="H18" s="35"/>
+      <c r="I18" s="34" t="n">
         <f aca="false">SUM(C18:H18)</f>
         <v>0</v>
       </c>
-      <c r="J18" s="31"/>
-      <c r="K18" s="0" t="n">
+      <c r="J18" s="32"/>
+      <c r="K18" s="1" t="n">
         <f aca="true" t="array" ref="K18:K18">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*1.5*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*1.5*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*1.5*24)</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="27" t="str">
+      <c r="A19" s="28" t="str">
         <f aca="false">IF(B19&gt;0,PROPER(TEXT(B19,"dddd")),"")</f>
         <v>Jueves</v>
       </c>
-      <c r="B19" s="32" t="n">
+      <c r="B19" s="33" t="n">
         <v>46156</v>
       </c>
-      <c r="C19" s="33"/>
-      <c r="D19" s="34"/>
-      <c r="E19" s="33"/>
-      <c r="F19" s="34"/>
-      <c r="G19" s="33"/>
-      <c r="H19" s="34"/>
-      <c r="I19" s="33" t="n">
+      <c r="C19" s="34"/>
+      <c r="D19" s="35"/>
+      <c r="E19" s="34"/>
+      <c r="F19" s="35"/>
+      <c r="G19" s="34"/>
+      <c r="H19" s="35"/>
+      <c r="I19" s="34" t="n">
         <f aca="false">SUM(C19:H19)</f>
         <v>0</v>
       </c>
-      <c r="J19" s="31"/>
-      <c r="K19" s="0" t="n">
+      <c r="J19" s="32"/>
+      <c r="K19" s="1" t="n">
         <f aca="true" t="array" ref="K19:K19">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*1.5*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*1.5*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*1.5*24)</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="27" t="str">
+      <c r="A20" s="28" t="str">
         <f aca="false">IF(B20&gt;0,PROPER(TEXT(B20,"dddd")),"")</f>
         <v>Viernes</v>
       </c>
-      <c r="B20" s="32" t="n">
+      <c r="B20" s="33" t="n">
         <v>46157</v>
       </c>
-      <c r="C20" s="33"/>
-      <c r="D20" s="34"/>
-      <c r="E20" s="33"/>
-      <c r="F20" s="34"/>
-      <c r="G20" s="33"/>
-      <c r="H20" s="34"/>
-      <c r="I20" s="33" t="n">
+      <c r="C20" s="34"/>
+      <c r="D20" s="35"/>
+      <c r="E20" s="34"/>
+      <c r="F20" s="35"/>
+      <c r="G20" s="34"/>
+      <c r="H20" s="35"/>
+      <c r="I20" s="34" t="n">
         <f aca="false">SUM(C20:H20)</f>
         <v>0</v>
       </c>
-      <c r="J20" s="31"/>
-      <c r="K20" s="0" t="n">
+      <c r="J20" s="32"/>
+      <c r="K20" s="1" t="n">
         <f aca="true" t="array" ref="K20:K20">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*1.5*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*1.5*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*1.5*24)</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="27" t="str">
+      <c r="A21" s="28" t="str">
         <f aca="false">IF(B21&gt;0,PROPER(TEXT(B21,"dddd")),"")</f>
         <v>Sábado</v>
       </c>
-      <c r="B21" s="28" t="n">
+      <c r="B21" s="29" t="n">
         <v>46158</v>
       </c>
-      <c r="C21" s="33"/>
-      <c r="D21" s="34"/>
-      <c r="E21" s="33"/>
-      <c r="F21" s="34"/>
-      <c r="G21" s="33"/>
-      <c r="H21" s="34"/>
-      <c r="I21" s="33" t="n">
+      <c r="C21" s="34"/>
+      <c r="D21" s="35"/>
+      <c r="E21" s="34"/>
+      <c r="F21" s="35"/>
+      <c r="G21" s="34"/>
+      <c r="H21" s="35"/>
+      <c r="I21" s="34" t="n">
         <f aca="false">SUM(C21:H21)</f>
         <v>0</v>
       </c>
-      <c r="J21" s="31"/>
-      <c r="K21" s="0" t="n">
+      <c r="J21" s="32"/>
+      <c r="K21" s="1" t="n">
         <f aca="true" t="array" ref="K21:K21">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*2*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*2*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*2*24)</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="27" t="str">
+      <c r="A22" s="28" t="str">
         <f aca="false">IF(B22&gt;0,PROPER(TEXT(B22,"dddd")),"")</f>
         <v>Domingo</v>
       </c>
-      <c r="B22" s="32" t="n">
+      <c r="B22" s="33" t="n">
         <v>46159</v>
       </c>
-      <c r="C22" s="33"/>
-      <c r="D22" s="34"/>
-      <c r="E22" s="33"/>
-      <c r="F22" s="34"/>
-      <c r="G22" s="33"/>
-      <c r="H22" s="34"/>
-      <c r="I22" s="33" t="n">
+      <c r="C22" s="34"/>
+      <c r="D22" s="35"/>
+      <c r="E22" s="34"/>
+      <c r="F22" s="35"/>
+      <c r="G22" s="34"/>
+      <c r="H22" s="35"/>
+      <c r="I22" s="34" t="n">
         <f aca="false">SUM(C22:H22)</f>
         <v>0</v>
       </c>
-      <c r="J22" s="31"/>
-      <c r="K22" s="0" t="n">
+      <c r="J22" s="32"/>
+      <c r="K22" s="1" t="n">
         <f aca="true" t="array" ref="K22:K22">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*2*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*2*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*2*24)</f>
         <v>0</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="27" t="str">
+      <c r="A23" s="28" t="str">
         <f aca="false">IF(B23&gt;0,PROPER(TEXT(B23,"dddd")),"")</f>
         <v>Lunes</v>
       </c>
-      <c r="B23" s="32" t="n">
+      <c r="B23" s="33" t="n">
         <v>46160</v>
       </c>
-      <c r="C23" s="33"/>
-      <c r="D23" s="34"/>
-      <c r="E23" s="33"/>
-      <c r="F23" s="34"/>
-      <c r="G23" s="33"/>
-      <c r="H23" s="34"/>
-      <c r="I23" s="33" t="n">
+      <c r="C23" s="34"/>
+      <c r="D23" s="35"/>
+      <c r="E23" s="34"/>
+      <c r="F23" s="35"/>
+      <c r="G23" s="34"/>
+      <c r="H23" s="35"/>
+      <c r="I23" s="34" t="n">
         <f aca="false">SUM(C23:H23)</f>
         <v>0</v>
       </c>
-      <c r="J23" s="31"/>
-      <c r="K23" s="0" t="n">
+      <c r="J23" s="32"/>
+      <c r="K23" s="1" t="n">
         <f aca="true" t="array" ref="K23:K23">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*1.5*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*1.5*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*1.5*24)</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="27" t="str">
+      <c r="A24" s="28" t="str">
         <f aca="false">IF(B24&gt;0,PROPER(TEXT(B24,"dddd")),"")</f>
         <v>Martes</v>
       </c>
-      <c r="B24" s="28" t="n">
+      <c r="B24" s="29" t="n">
         <v>46161</v>
       </c>
-      <c r="C24" s="33"/>
-      <c r="D24" s="34"/>
-      <c r="E24" s="33"/>
-      <c r="F24" s="34"/>
-      <c r="G24" s="33"/>
-      <c r="H24" s="34"/>
-      <c r="I24" s="33" t="n">
+      <c r="C24" s="34"/>
+      <c r="D24" s="35"/>
+      <c r="E24" s="34"/>
+      <c r="F24" s="35"/>
+      <c r="G24" s="34"/>
+      <c r="H24" s="35"/>
+      <c r="I24" s="34" t="n">
         <f aca="false">SUM(C24:H24)</f>
         <v>0</v>
       </c>
-      <c r="J24" s="31"/>
-      <c r="K24" s="0" t="n">
+      <c r="J24" s="32"/>
+      <c r="K24" s="1" t="n">
         <f aca="true" t="array" ref="K24:K24">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*1.5*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*1.5*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*1.5*24)</f>
         <v>0</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="27" t="str">
+      <c r="A25" s="28" t="str">
         <f aca="false">IF(B25&gt;0,PROPER(TEXT(B25,"dddd")),"")</f>
         <v>Miércoles</v>
       </c>
-      <c r="B25" s="32" t="n">
+      <c r="B25" s="33" t="n">
         <v>46162</v>
       </c>
-      <c r="C25" s="33"/>
-      <c r="D25" s="34"/>
-      <c r="E25" s="33"/>
-      <c r="F25" s="34"/>
-      <c r="G25" s="33"/>
-      <c r="H25" s="34"/>
-      <c r="I25" s="33" t="n">
+      <c r="C25" s="34"/>
+      <c r="D25" s="35"/>
+      <c r="E25" s="34"/>
+      <c r="F25" s="35"/>
+      <c r="G25" s="34"/>
+      <c r="H25" s="35"/>
+      <c r="I25" s="34" t="n">
         <f aca="false">SUM(C25:H25)</f>
         <v>0</v>
       </c>
-      <c r="J25" s="31"/>
-      <c r="K25" s="0" t="n">
+      <c r="J25" s="32"/>
+      <c r="K25" s="1" t="n">
         <f aca="true" t="array" ref="K25:K25">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*1.5*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*1.5*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*1.5*24)</f>
         <v>0</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="27" t="str">
+      <c r="A26" s="28" t="str">
         <f aca="false">IF(B26&gt;0,PROPER(TEXT(B26,"dddd")),"")</f>
         <v>Jueves</v>
       </c>
-      <c r="B26" s="32" t="n">
+      <c r="B26" s="33" t="n">
         <v>46163</v>
       </c>
-      <c r="C26" s="33"/>
-      <c r="D26" s="34"/>
-      <c r="E26" s="33"/>
-      <c r="F26" s="34"/>
-      <c r="G26" s="33"/>
-      <c r="H26" s="34"/>
-      <c r="I26" s="33" t="n">
+      <c r="C26" s="34"/>
+      <c r="D26" s="35"/>
+      <c r="E26" s="34"/>
+      <c r="F26" s="35"/>
+      <c r="G26" s="34"/>
+      <c r="H26" s="35"/>
+      <c r="I26" s="34" t="n">
         <f aca="false">SUM(C26:H26)</f>
         <v>0</v>
       </c>
-      <c r="J26" s="31"/>
-      <c r="K26" s="0" t="n">
+      <c r="J26" s="32"/>
+      <c r="K26" s="1" t="n">
         <f aca="true" t="array" ref="K26:K26">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*1.5*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*1.5*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*1.5*24)</f>
         <v>0</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="27" t="str">
+      <c r="A27" s="28" t="str">
         <f aca="false">IF(B27&gt;0,PROPER(TEXT(B27,"dddd")),"")</f>
         <v>Viernes</v>
       </c>
-      <c r="B27" s="28" t="n">
+      <c r="B27" s="29" t="n">
         <v>46164</v>
       </c>
-      <c r="C27" s="33"/>
-      <c r="D27" s="34"/>
-      <c r="E27" s="33"/>
-      <c r="F27" s="34"/>
-      <c r="G27" s="33"/>
-      <c r="H27" s="34"/>
-      <c r="I27" s="33" t="n">
+      <c r="C27" s="34"/>
+      <c r="D27" s="35"/>
+      <c r="E27" s="34"/>
+      <c r="F27" s="35"/>
+      <c r="G27" s="34"/>
+      <c r="H27" s="35"/>
+      <c r="I27" s="34" t="n">
         <f aca="false">SUM(C27:H27)</f>
         <v>0</v>
       </c>
-      <c r="J27" s="31"/>
-      <c r="K27" s="0" t="n">
+      <c r="J27" s="32"/>
+      <c r="K27" s="1" t="n">
         <f aca="true" t="array" ref="K27:K27">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*1.5*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*1.5*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*1.5*24)</f>
         <v>0</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="27" t="str">
+      <c r="A28" s="28" t="str">
         <f aca="false">IF(B28&gt;0,PROPER(TEXT(B28,"dddd")),"")</f>
         <v>Sábado</v>
       </c>
-      <c r="B28" s="32" t="n">
+      <c r="B28" s="33" t="n">
         <v>46165</v>
       </c>
-      <c r="C28" s="33"/>
-      <c r="D28" s="34"/>
-      <c r="E28" s="33"/>
-      <c r="F28" s="34"/>
-      <c r="G28" s="33"/>
-      <c r="H28" s="34"/>
-      <c r="I28" s="33" t="n">
+      <c r="C28" s="34"/>
+      <c r="D28" s="35"/>
+      <c r="E28" s="34"/>
+      <c r="F28" s="35"/>
+      <c r="G28" s="34"/>
+      <c r="H28" s="35"/>
+      <c r="I28" s="34" t="n">
         <f aca="false">SUM(C28:H28)</f>
         <v>0</v>
       </c>
-      <c r="J28" s="31"/>
-      <c r="K28" s="0" t="n">
+      <c r="J28" s="32"/>
+      <c r="K28" s="1" t="n">
         <f aca="true" t="array" ref="K28:K28">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*2*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*2*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*2*24)</f>
         <v>0</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="27" t="str">
+      <c r="A29" s="28" t="str">
         <f aca="false">IF(B29&gt;0,PROPER(TEXT(B29,"dddd")),"")</f>
         <v>Domingo</v>
       </c>
-      <c r="B29" s="32" t="n">
+      <c r="B29" s="33" t="n">
         <v>46166</v>
       </c>
-      <c r="C29" s="33"/>
-      <c r="D29" s="34"/>
-      <c r="E29" s="33"/>
-      <c r="F29" s="34"/>
-      <c r="G29" s="33"/>
-      <c r="H29" s="34"/>
-      <c r="I29" s="33" t="n">
+      <c r="C29" s="34"/>
+      <c r="D29" s="35"/>
+      <c r="E29" s="34"/>
+      <c r="F29" s="35"/>
+      <c r="G29" s="34"/>
+      <c r="H29" s="35"/>
+      <c r="I29" s="34" t="n">
         <f aca="false">SUM(C29:H29)</f>
         <v>0</v>
       </c>
-      <c r="J29" s="31"/>
-      <c r="K29" s="0" t="n">
+      <c r="J29" s="32"/>
+      <c r="K29" s="1" t="n">
         <f aca="true" t="array" ref="K29:K29">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*2*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*2*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*2*24)</f>
         <v>0</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="27" t="str">
+      <c r="A30" s="28" t="str">
         <f aca="false">IF(B30&gt;0,PROPER(TEXT(B30,"dddd")),"")</f>
         <v>Lunes</v>
       </c>
-      <c r="B30" s="28" t="n">
+      <c r="B30" s="29" t="n">
         <v>46167</v>
       </c>
-      <c r="C30" s="33"/>
-      <c r="D30" s="34"/>
-      <c r="E30" s="33"/>
-      <c r="F30" s="34"/>
-      <c r="G30" s="33"/>
-      <c r="H30" s="34"/>
-      <c r="I30" s="33" t="n">
+      <c r="C30" s="34"/>
+      <c r="D30" s="35"/>
+      <c r="E30" s="34"/>
+      <c r="F30" s="35"/>
+      <c r="G30" s="34"/>
+      <c r="H30" s="35"/>
+      <c r="I30" s="34" t="n">
         <f aca="false">SUM(C30:H30)</f>
         <v>0</v>
       </c>
-      <c r="J30" s="31"/>
-      <c r="K30" s="0" t="n">
+      <c r="J30" s="32"/>
+      <c r="K30" s="1" t="n">
         <f aca="true" t="array" ref="K30:K30">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*2*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*2*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*2*24)</f>
         <v>0</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="27" t="str">
+      <c r="A31" s="28" t="str">
         <f aca="false">IF(B31&gt;0,PROPER(TEXT(B31,"dddd")),"")</f>
         <v>Martes</v>
       </c>
-      <c r="B31" s="32" t="n">
+      <c r="B31" s="33" t="n">
         <v>46168</v>
       </c>
-      <c r="C31" s="33"/>
-      <c r="D31" s="34"/>
-      <c r="E31" s="33"/>
-      <c r="F31" s="34"/>
-      <c r="G31" s="33"/>
-      <c r="H31" s="34"/>
-      <c r="I31" s="33" t="n">
+      <c r="C31" s="34"/>
+      <c r="D31" s="35"/>
+      <c r="E31" s="34"/>
+      <c r="F31" s="35"/>
+      <c r="G31" s="34"/>
+      <c r="H31" s="35"/>
+      <c r="I31" s="34" t="n">
         <f aca="false">SUM(C31:H31)</f>
         <v>0</v>
       </c>
-      <c r="J31" s="31"/>
-      <c r="K31" s="0" t="n">
+      <c r="J31" s="32"/>
+      <c r="K31" s="1" t="n">
         <f aca="true" t="array" ref="K31:K31">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*1.5*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*1.5*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*1.5*24)</f>
         <v>0</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="27" t="str">
+      <c r="A32" s="28" t="str">
         <f aca="false">IF(B32&gt;0,PROPER(TEXT(B32,"dddd")),"")</f>
         <v>Miércoles</v>
       </c>
-      <c r="B32" s="32" t="n">
+      <c r="B32" s="33" t="n">
         <v>46169</v>
       </c>
-      <c r="C32" s="33"/>
-      <c r="D32" s="34"/>
-      <c r="E32" s="33"/>
-      <c r="F32" s="34"/>
-      <c r="G32" s="33"/>
-      <c r="H32" s="34"/>
-      <c r="I32" s="33" t="n">
+      <c r="C32" s="34"/>
+      <c r="D32" s="35"/>
+      <c r="E32" s="34"/>
+      <c r="F32" s="35"/>
+      <c r="G32" s="34"/>
+      <c r="H32" s="35"/>
+      <c r="I32" s="34" t="n">
         <f aca="false">SUM(C32:H32)</f>
         <v>0</v>
       </c>
-      <c r="J32" s="31"/>
-      <c r="K32" s="0" t="n">
+      <c r="J32" s="32"/>
+      <c r="K32" s="1" t="n">
         <f aca="true" t="array" ref="K32:K32">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*1.5*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*1.5*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*1.5*24)</f>
         <v>0</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="27" t="str">
+      <c r="A33" s="28" t="str">
         <f aca="false">IF(B33&gt;0,PROPER(TEXT(B33,"dddd")),"")</f>
         <v>Jueves</v>
       </c>
-      <c r="B33" s="28" t="n">
+      <c r="B33" s="29" t="n">
         <v>46170</v>
       </c>
-      <c r="C33" s="33"/>
-      <c r="D33" s="34"/>
-      <c r="E33" s="33"/>
-      <c r="F33" s="34"/>
-      <c r="G33" s="33"/>
-      <c r="H33" s="34"/>
-      <c r="I33" s="33" t="n">
+      <c r="C33" s="34"/>
+      <c r="D33" s="35"/>
+      <c r="E33" s="34"/>
+      <c r="F33" s="35"/>
+      <c r="G33" s="34"/>
+      <c r="H33" s="35"/>
+      <c r="I33" s="34" t="n">
         <f aca="false">SUM(C33:H33)</f>
         <v>0</v>
       </c>
-      <c r="J33" s="31"/>
-      <c r="K33" s="0" t="n">
+      <c r="J33" s="32"/>
+      <c r="K33" s="1" t="n">
         <f aca="true" t="array" ref="K33:K33">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*1.5*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*1.5*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*1.5*24)</f>
         <v>0</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="27" t="str">
+      <c r="A34" s="28" t="str">
         <f aca="false">IF(B34&gt;0,PROPER(TEXT(B34,"dddd")),"")</f>
         <v>Viernes</v>
       </c>
-      <c r="B34" s="32" t="n">
+      <c r="B34" s="33" t="n">
         <v>46171</v>
       </c>
-      <c r="C34" s="33"/>
-      <c r="D34" s="34"/>
-      <c r="E34" s="33"/>
-      <c r="F34" s="34"/>
-      <c r="G34" s="33"/>
-      <c r="H34" s="34"/>
-      <c r="I34" s="33" t="n">
+      <c r="C34" s="34"/>
+      <c r="D34" s="35"/>
+      <c r="E34" s="34"/>
+      <c r="F34" s="35"/>
+      <c r="G34" s="34"/>
+      <c r="H34" s="35"/>
+      <c r="I34" s="34" t="n">
         <f aca="false">SUM(C34:H34)</f>
         <v>0</v>
       </c>
-      <c r="J34" s="31"/>
-      <c r="K34" s="0" t="n">
+      <c r="J34" s="32"/>
+      <c r="K34" s="1" t="n">
         <f aca="true" t="array" ref="K34:K34">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*1.5*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*1.5*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*1.5*24)</f>
         <v>0</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="27" t="str">
+      <c r="A35" s="28" t="str">
         <f aca="false">IF(B35&gt;0,PROPER(TEXT(B35,"dddd")),"")</f>
         <v>Sábado</v>
       </c>
-      <c r="B35" s="32" t="n">
+      <c r="B35" s="33" t="n">
         <v>46172</v>
       </c>
-      <c r="C35" s="33"/>
-      <c r="D35" s="34"/>
-      <c r="E35" s="33"/>
-      <c r="F35" s="34"/>
-      <c r="G35" s="33"/>
-      <c r="H35" s="34"/>
-      <c r="I35" s="33" t="n">
+      <c r="C35" s="34"/>
+      <c r="D35" s="35"/>
+      <c r="E35" s="34"/>
+      <c r="F35" s="35"/>
+      <c r="G35" s="34"/>
+      <c r="H35" s="35"/>
+      <c r="I35" s="34" t="n">
         <f aca="false">SUM(C35:H35)</f>
         <v>0</v>
       </c>
-      <c r="J35" s="31"/>
-      <c r="K35" s="0" t="n">
+      <c r="J35" s="32"/>
+      <c r="K35" s="1" t="n">
         <f aca="true" t="array" ref="K35:K35">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*2*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*2*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*2*24)</f>
         <v>0</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="37" t="str">
+      <c r="A36" s="38" t="str">
         <f aca="false">IF(B36&gt;0,PROPER(TEXT(B36,"dddd")),"")</f>
         <v/>
       </c>
-      <c r="B36" s="38"/>
-      <c r="C36" s="39"/>
-      <c r="D36" s="40"/>
-      <c r="E36" s="39"/>
-      <c r="F36" s="40"/>
-      <c r="G36" s="39"/>
-      <c r="H36" s="40"/>
-      <c r="I36" s="39" t="n">
+      <c r="B36" s="39"/>
+      <c r="C36" s="40"/>
+      <c r="D36" s="41"/>
+      <c r="E36" s="40"/>
+      <c r="F36" s="41"/>
+      <c r="G36" s="40"/>
+      <c r="H36" s="41"/>
+      <c r="I36" s="40" t="n">
         <f aca="false">SUM(C36:H36)</f>
         <v>0</v>
       </c>
-      <c r="J36" s="41"/>
-      <c r="K36" s="0" t="n">
-        <f aca="true" t="array" ref="K36:K36">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*2*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*2*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*2*24)</f>
-        <v>0</v>
-      </c>
+      <c r="J36" s="42"/>
     </row>
     <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="42"/>
-      <c r="B37" s="43"/>
-      <c r="C37" s="43"/>
-      <c r="D37" s="43"/>
-      <c r="E37" s="43"/>
-      <c r="F37" s="43"/>
-      <c r="G37" s="43"/>
-      <c r="H37" s="43"/>
-      <c r="I37" s="44"/>
-      <c r="J37" s="43"/>
+      <c r="A37" s="43"/>
+      <c r="B37" s="44"/>
+      <c r="C37" s="44"/>
+      <c r="D37" s="44"/>
+      <c r="E37" s="44"/>
+      <c r="F37" s="44"/>
+      <c r="G37" s="44"/>
+      <c r="H37" s="44"/>
+      <c r="I37" s="45"/>
+      <c r="J37" s="44"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/models/plantilla_informe_he.xlsx
+++ b/models/plantilla_informe_he.xlsx
@@ -817,9 +817,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>109080</xdr:colOff>
+      <xdr:colOff>108720</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>1054080</xdr:rowOff>
+      <xdr:rowOff>1053720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -833,7 +833,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="2038320" cy="1054080"/>
+          <a:ext cx="2037960" cy="1053720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -855,9 +855,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>7869960</xdr:colOff>
+      <xdr:colOff>7869600</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>399600</xdr:rowOff>
+      <xdr:rowOff>399240</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -871,7 +871,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="10010520" y="21960"/>
-          <a:ext cx="4149720" cy="377640"/>
+          <a:ext cx="4149360" cy="377280"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1006,7 +1006,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="3" style="1" width="6.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="2" width="9.9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="101.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="7.9"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="11" min="11" style="1" width="7.9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="8.6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="12.2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="3.3"/>
